--- a/Indomie Clients Details/Gourmet/Gourmet - 20+1 .xlsx
+++ b/Indomie Clients Details/Gourmet/Gourmet - 20+1 .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83B6EE6-17A9-4B39-8BE4-9BF7647B891F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A47D5D-F5FF-46ED-AD06-9C96D9B32D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,7 +3895,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -3923,7 +3923,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -4347,11 +4347,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -4360,23 +4360,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100">
         <v>0</v>
@@ -4753,11 +4753,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -4766,23 +4766,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4832,7 +4832,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4853,7 +4853,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4896,7 +4896,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4943,7 +4943,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4978,7 +4978,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5150,7 +5150,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -5178,7 +5178,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -5598,11 +5598,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -5611,23 +5611,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100"/>
     </row>
@@ -5994,11 +5994,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -6007,23 +6007,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6073,7 +6073,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6094,7 +6094,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6137,7 +6137,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6184,7 +6184,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6219,7 +6219,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6391,7 +6391,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -6419,7 +6419,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -6839,11 +6839,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -6852,23 +6852,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100"/>
     </row>
@@ -7234,11 +7234,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -7247,23 +7247,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7313,7 +7313,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7334,7 +7334,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7377,7 +7377,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7424,7 +7424,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7459,7 +7459,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7631,7 +7631,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -7659,7 +7659,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -8083,11 +8083,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -8096,23 +8096,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100">
         <v>0</v>
@@ -8490,11 +8490,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -8503,23 +8503,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -8569,7 +8569,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8590,7 +8590,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8633,7 +8633,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8680,7 +8680,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8715,7 +8715,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8887,7 +8887,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -8915,7 +8915,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -10142,7 +10142,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -10170,7 +10170,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -11442,7 +11442,7 @@
       <c r="M4" s="350"/>
       <c r="N4" s="351">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="351"/>
       <c r="P4" s="351"/>
@@ -11476,7 +11476,7 @@
       <c r="M5" s="350"/>
       <c r="N5" s="351">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="349"/>
       <c r="P5" s="349"/>
@@ -12812,7 +12812,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -12840,7 +12840,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -14067,7 +14067,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -14095,7 +14095,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -15322,7 +15322,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -15350,7 +15350,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -19327,7 +19327,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -19355,7 +19355,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -20582,7 +20582,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -20610,7 +20610,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -21837,7 +21837,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -21865,7 +21865,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -23092,7 +23092,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -23120,7 +23120,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -24334,7 +24334,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -24355,7 +24355,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -25531,7 +25531,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -25552,7 +25552,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -26733,7 +26733,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -26754,7 +26754,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -27933,7 +27933,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -27954,7 +27954,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -29135,7 +29135,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -29156,7 +29156,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -30335,7 +30335,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -30355,7 +30355,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -31539,7 +31539,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -31567,7 +31567,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="U15" s="163">
         <f>+'2'!P35</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="U16" s="163">
         <f>+'4'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="U17" s="163">
         <f>+'3'!P35</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -32012,11 +32012,11 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18</f>
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>25182</v>
+        <v>0</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
@@ -32028,23 +32028,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>4532.7599999999993</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>20649.240000000002</v>
+        <v>0</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>3716.8632000000007</v>
+        <v>0</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>121.83051599999996</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>24487.933716</v>
+        <v>0</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="U18" s="163">
         <f>+'5'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -32122,7 +32122,7 @@
       </c>
       <c r="U19" s="163">
         <f>+'6'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -32192,7 +32192,7 @@
       </c>
       <c r="U20" s="163">
         <f>+'7'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="21" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -32262,7 +32262,7 @@
       </c>
       <c r="U21" s="163">
         <f>+'8'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -32332,7 +32332,7 @@
       </c>
       <c r="U22" s="163">
         <f>+'9'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="23" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="U23" s="163">
         <f>+'10'!P35</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="24" spans="1:21 16384:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
@@ -32482,7 +32482,7 @@
       <c r="B25" s="305"/>
       <c r="C25" s="306">
         <f>H25/40</f>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D25" s="300"/>
       <c r="E25" s="300"/>
@@ -32493,11 +32493,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>2880</v>
+        <v>2400</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>180147.59999999998</v>
+        <v>154965.59999999998</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -32509,23 +32509,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>32426.567999999992</v>
+        <v>27893.807999999994</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>147721.03199999998</v>
+        <v>127071.79199999999</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>26589.785760000006</v>
+        <v>22872.922560000003</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>871.55408879999982</v>
+        <v>749.72357279999994</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>175182.37184880002</v>
+        <v>150694.43813280002</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -32985,7 +32985,7 @@
       </c>
       <c r="U42" s="164">
         <f>SUM(U14:U40)</f>
-        <v>175182.37184880004</v>
+        <v>150694.43813280005</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -33018,7 +33018,7 @@
       <c r="O44" s="317"/>
       <c r="P44" s="151">
         <f>I25</f>
-        <v>180147.59999999998</v>
+        <v>154965.59999999998</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33039,7 +33039,7 @@
       <c r="O45" s="319"/>
       <c r="P45" s="152">
         <f>L25</f>
-        <v>32426.567999999992</v>
+        <v>27893.807999999994</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33082,7 +33082,7 @@
       <c r="O47" s="319"/>
       <c r="P47" s="152">
         <f>P44-P45-P46</f>
-        <v>147721.03199999998</v>
+        <v>127071.79199999999</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P48" s="152">
         <f>N25</f>
-        <v>26589.785760000006</v>
+        <v>22872.922560000003</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33129,7 +33129,7 @@
       <c r="O49" s="321"/>
       <c r="P49" s="152">
         <f>P47+P48</f>
-        <v>174310.81775999998</v>
+        <v>149944.71455999999</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33154,7 +33154,7 @@
       </c>
       <c r="P50" s="152">
         <f>O50*P49</f>
-        <v>4357.7704439999998</v>
+        <v>3748.6178639999998</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33164,7 +33164,7 @@
       <c r="O51" s="299"/>
       <c r="P51" s="159">
         <f>P49+P50</f>
-        <v>178668.58820399997</v>
+        <v>153693.33242399999</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -33322,7 +33322,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -33342,7 +33342,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -34600,7 +34600,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -34628,7 +34628,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -35052,11 +35052,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -35065,23 +35065,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="114">
         <v>0</v>
@@ -35458,11 +35458,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -35471,23 +35471,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -35537,7 +35537,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35558,7 +35558,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35601,7 +35601,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35626,7 +35626,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35648,7 +35648,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35683,7 +35683,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -35855,7 +35855,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -35883,7 +35883,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -36307,11 +36307,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -36320,23 +36320,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>755.45999999999992</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>3441.54</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>619.47719999999993</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>20.305085999999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>4081.3222859999996</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="114">
         <v>0</v>
@@ -36714,11 +36714,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -36727,23 +36727,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>24620.172000000002</v>
+        <v>21178.632000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>145.25901479999999</v>
+        <v>124.9539288</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>29197.061974799995</v>
+        <v>25115.7396888</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -36793,7 +36793,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36814,7 +36814,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36857,7 +36857,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>24620.172000000002</v>
+        <v>21178.632000000005</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36882,7 +36882,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36904,7 +36904,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>29051.802960000001</v>
+        <v>24990.785760000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36929,7 +36929,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>145.25901480000002</v>
+        <v>124.95392880000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36939,7 +36939,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -37111,7 +37111,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -37139,7 +37139,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -37563,11 +37563,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -37576,23 +37576,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>755.45999999999992</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>3441.54</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>619.47719999999993</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>20.305085999999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>4081.3222859999996</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="114">
         <v>0</v>
@@ -37969,11 +37969,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -37982,23 +37982,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>24620.172000000002</v>
+        <v>21178.632000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>145.25901479999999</v>
+        <v>124.9539288</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>29197.061974799995</v>
+        <v>25115.7396888</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -38048,7 +38048,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -38069,7 +38069,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -38112,7 +38112,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>24620.172000000002</v>
+        <v>21178.632000000005</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -38159,7 +38159,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>29051.802960000001</v>
+        <v>24990.785760000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -38184,7 +38184,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>145.25901480000002</v>
+        <v>124.95392880000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -38194,7 +38194,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -38365,7 +38365,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -38393,7 +38393,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -38817,11 +38817,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -38830,23 +38830,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100">
         <v>0</v>
@@ -39223,11 +39223,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -39236,23 +39236,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -39302,7 +39302,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -39323,7 +39323,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -39366,7 +39366,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -39391,7 +39391,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -39413,7 +39413,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -39438,7 +39438,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -39448,7 +39448,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39620,7 +39620,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -39648,7 +39648,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -40072,11 +40072,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -40085,23 +40085,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100">
         <v>0</v>
@@ -40479,11 +40479,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -40492,23 +40492,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -40558,7 +40558,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -40579,7 +40579,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -40622,7 +40622,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -40647,7 +40647,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -40669,7 +40669,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -40694,7 +40694,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -40704,7 +40704,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40876,7 +40876,7 @@
       <c r="M4" s="324"/>
       <c r="N4" s="338">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="338"/>
       <c r="P4" s="338"/>
@@ -40904,7 +40904,7 @@
       <c r="M5" s="324"/>
       <c r="N5" s="338">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="325"/>
       <c r="P5" s="325"/>
@@ -41328,11 +41328,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="100">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -41341,23 +41341,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>309.73859999999996</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>10.152543</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>2040.6611429999998</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="100">
         <v>0</v>
@@ -41734,11 +41734,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -41747,23 +41747,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>12310.086000000001</v>
+        <v>10589.316000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>72.629507399999994</v>
+        <v>62.4769644</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14598.530987399998</v>
+        <v>12557.8698444</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -41813,7 +41813,7 @@
       <c r="O28" s="317"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>12913.800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -41834,7 +41834,7 @@
       <c r="O29" s="319"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2702.2139999999995</v>
+        <v>2324.4839999999995</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -41877,7 +41877,7 @@
       <c r="O31" s="319"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>10589.316000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -41902,7 +41902,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2215.8154799999998</v>
+        <v>1906.0768799999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -41924,7 +41924,7 @@
       <c r="O33" s="321"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14525.90148</v>
+        <v>12495.392880000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -41949,7 +41949,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>72.629507400000008</v>
+        <v>62.476964400000014</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -41959,7 +41959,7 @@
       <c r="O35" s="299"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14598.530987400001</v>
+        <v>12557.869844400004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
